--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,23 +476,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tsla</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>427.85</v>
+        <v>449.31</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -516,11 +516,266 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-12 19:59</t>
+          <t>2026-05-14 18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1006.34</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>235.29</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>396.06</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>65</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>298.17</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1034.25</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:43</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>449.31</v>
+        <v>228.52</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-14 18:43</t>
+          <t>2026-05-15 18:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1006.34</v>
+        <v>432.25</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-14 18:43</t>
+          <t>2026-05-15 18:47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>235.29</v>
+        <v>440.04</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -614,26 +614,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.68</v>
+        <v>1.08</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-14 18:43</t>
+          <t>2026-05-15 18:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>396.06</v>
+        <v>286.31</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.37</v>
+        <v>0.54</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-14 18:43</t>
+          <t>2026-05-15 18:47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>298.17</v>
+        <v>1833.98</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-14 18:43</t>
+          <t>2026-05-15 18:47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1034.25</v>
+        <v>735.8200000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -771,11 +771,62 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.29</v>
+        <v>0.65</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-14 18:43</t>
+          <t>2026-05-15 18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>117.04</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-15 18:47</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>228.52</v>
+        <v>1002.03</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-15 18:47</t>
+          <t>2026-05-15 18:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>432.25</v>
+        <v>228.06</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-15 18:47</t>
+          <t>2026-05-15 18:58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>440.04</v>
+        <v>392.36</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -614,26 +614,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-15 18:47</t>
+          <t>2026-05-15 18:58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>286.31</v>
+        <v>302.58</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-15 18:47</t>
+          <t>2026-05-15 18:58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1833.98</v>
+        <v>1046.32</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -720,113 +720,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-15 18:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>735.8200000000001</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>COMPRA FUERTE</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-05-15 18:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>117.04</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>COMPRA FUERTE</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>65</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-05-15 18:47</t>
+          <t>2026-05-15 18:58</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,28 +476,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>SAB.MC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1021.41</v>
+        <v>3.29</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -507,31 +507,31 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.23</v>
+        <v>0.26</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-20 12:38</t>
+          <t>2026-05-20 13:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>SAN.MC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1094.32</v>
+        <v>10.29</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -563,66 +563,4503 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.61</v>
+        <v>0.11</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-20 12:39</t>
+          <t>2026-05-20 13:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>298.97</v>
+        <v>19.08</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LDA.MC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CABK.MC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MAP.MC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UNI.MC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BKT.MC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GSJ.MC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HLZ.MC</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MEL.MC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MTS.MC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NTGY.MC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>COMPRA FUERTE</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D14" t="n">
         <v>65</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>COMPRANDO</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-05-20 12:39</t>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OLE.MC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORY.MC</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PAR.MC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PSG.MC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>65</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SLR.MC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SOL.MC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TLGO.MC</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TRE.MC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TRG.MC</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TUB.MC</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>XPBR.MC</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ALNT.MC</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ATRY.MC</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CLR.MC</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>COXE.MC</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>25</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A3M.MC</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACX.MC</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AEDAS.MC</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ALB.MC</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>169</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ALM.MC</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AMS.MC</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AZK.MC</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>50</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CAF.MC</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CBAV.MC</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CCEP.MC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CIE.MC</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CLNX.MC</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>65</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DOM.MC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ENO.MC</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HOME.MC</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ISUR.MC</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>25</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NEA.MC</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IDR.MC</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>40</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AIR.MC</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IAG.MC</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>25</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ACS.MC</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ANA.MC</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>249.2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AMP.MC</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>25</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ANE.MC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SCYR.MC</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GRE.MC</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>50</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ELE.MC</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GRF.MC</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>40</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FER.MC</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MRL.MC</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>REP.MC</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>40</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COL.MC</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>25</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TEF.MC</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>40</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ITX.MC</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>40</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ADX.MC</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FCC.MC</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>40</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RJF.MC</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>40</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VID.MC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>40</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AI.MC</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>25</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AENA.MC</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>25</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FAE.MC</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GEST.MC</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>15</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PHM.MC</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IBE.MC</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FDR.MC</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>40</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PUIG.MC</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>40</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LOG.MC</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>50</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ENG.MC</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>40</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ENC.MC</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ECR.MC</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EBRO.MC</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>RED.MC</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>25</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ROVI.MC</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BKY.MC</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>25</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>VIS.MC</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>25</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>OHLA.MC</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>IMC.MC</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>65</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NXT.MC</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>40</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SAI.MC</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EZE.MC</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>40</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1021.41</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>80</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>404.11</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>15</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:17</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,51 +476,816 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>DAN.MI</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>LLY</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1018.87</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>COMPRA FUERTE</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>65</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-05-21 12:46</t>
+      <c r="B3" t="n">
+        <v>1021.72</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>299.67</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1074.74</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>65</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SHEN</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SAN.MC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AZM.MI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IFX.DE</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>65</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1510.81</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SHEN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>255.01</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1021.63</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>299.73</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CGEO.L</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4095</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>127.01</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>65</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:22</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>LOG.MC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1063.5</v>
+        <v>33.82</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -512,26 +512,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.24</v>
+        <v>1.05</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-22 16:16</t>
+          <t>2026-05-26 16:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SAB.MC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>268.08</v>
+        <v>3.48</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.12</v>
+        <v>1.33</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-22 16:16</t>
+          <t>2026-05-26 16:06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GRE.MC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>309.14</v>
+        <v>133.4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -618,22 +618,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-22 16:16</t>
+          <t>2026-05-26 16:06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F8P</t>
+          <t>NHY.OL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.79</v>
+        <v>115.35</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,11 +669,4499 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-22 16:19</t>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CGEO.L</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4050</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INGA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>URW</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LUNR</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>65</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>311.46</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>132.68</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>380.17</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>226.32</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SATL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IFX.DE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SAN.MC</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ACX.MC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>65</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1626.64</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>65</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>154.45</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>65</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AZM.MI</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>65</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>65</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>307.39</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>65</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>65</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>268.05</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>65</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>311.12</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>65</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1066.43</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>65</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>156.43</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>65</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SCYR.MC</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UNI.MC</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BKT.MC</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0IE9</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ENEL.MI</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DAN.MI</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>OHB.DE</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>583</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>50</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>117.51</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>50</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ELG.DE</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RIO.L</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7941</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>112.93</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SYM</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>53.31</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>205.64</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>40</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DOCN</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>163.08</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>29</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>40</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>40</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CCI</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>40</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ANA.MC</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>260.4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>40</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>REP.MC</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>40</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ANE.MC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>40</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ABBN.SW</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>40</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>489.56</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>121.64</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>267.43</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>40</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>210.05</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>40</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DHI</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>145.77</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>40</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>447.69</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>40</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>857.12</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>40</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>243.05</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>40</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>255.83</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>40</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GNTX</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>609.71</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>40</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>129.98</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>40</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SHEN</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>40</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AMPX</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>40</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MAP.MC</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>25</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CBRS</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>240.71</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>25</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CABK.MC</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>25</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>OVS.MI</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>25</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ENR.DE</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>179.26</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>25</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>HOT.DE</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>485.8</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>194.64</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>429.04</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>25</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>524</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>25</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IGV</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>25</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MEL.MC</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>15</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MVC.MC</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>15</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ITX.MC</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>15</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OBDC</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>15</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>417.79</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>15</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>165.23</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>15</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EOSE</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>15</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>429.17</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>15</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BAM</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>15</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>281.41</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KODK</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:09</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LOG.MC</t>
+          <t>ACX.MC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.82</v>
+        <v>16.01</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -520,18 +520,18 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SAB.MC</t>
+          <t>LOG.MC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.48</v>
+        <v>33.7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-26 16:06</t>
+          <t>2026-05-26 16:47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRE.MC</t>
+          <t>SAN.MC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133.4</v>
+        <v>10.77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -618,22 +618,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-26 16:06</t>
+          <t>2026-05-26 16:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NHY.OL</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115.35</v>
+        <v>1633.34</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CGEO.L</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4050</v>
+        <v>154.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>AZM.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.88</v>
+        <v>35.53</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>URW</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>97.92</v>
+        <v>32.77</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.1</v>
+        <v>0.68</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44.56</v>
+        <v>312.03</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>311.46</v>
+        <v>878.17</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -924,22 +924,22 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>132.68</v>
+        <v>37.88</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>380.17</v>
+        <v>264.7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1026,22 +1026,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>226.32</v>
+        <v>311.2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1077,22 +1077,22 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SATL</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.93</v>
+        <v>1073.67</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1128,22 +1128,22 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77.48999999999999</v>
+        <v>158.06</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1179,30 +1179,30 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SAN.MC</t>
+          <t>BESI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10.75</v>
+        <v>287.8</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1230,30 +1230,30 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.3</v>
+        <v>0.53</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ACX.MC</t>
+          <t>DAN.MI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.97</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1281,30 +1281,30 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>OHB.DE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1626.64</v>
+        <v>578</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1332,30 +1332,30 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.25</v>
+        <v>0.73</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>154.45</v>
+        <v>117.35</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1383,30 +1383,30 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AZM.MI</t>
+          <t>ANA.MC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>35.44</v>
+        <v>259.2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1434,34 +1434,34 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>REP.MC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.44</v>
+        <v>22.13</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1485,34 +1485,34 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>ANE.MC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>307.39</v>
+        <v>24.18</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1536,30 +1536,30 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>ABBN.SW</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>37.98</v>
+        <v>85</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1587,30 +1587,30 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>268.05</v>
+        <v>490.45</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1638,30 +1638,30 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>311.12</v>
+        <v>123.02</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1689,34 +1689,34 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1066.43</v>
+        <v>269.46</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1740,30 +1740,30 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>156.43</v>
+        <v>204.08</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1791,34 +1791,34 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCYR.MC</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.7</v>
+        <v>146.08</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1842,30 +1842,30 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-05-26 16:06</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.07</v>
+        <v>453.2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1893,34 +1893,34 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-05-26 16:06</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UNI.MC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.87</v>
+        <v>250.11</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1944,34 +1944,34 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-05-26 16:06</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BKT.MC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>14.36</v>
+        <v>255.88</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1995,34 +1995,34 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-05-26 16:06</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0IE9</t>
+          <t>GNTX</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23.73</v>
+        <v>23.92</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2046,22 +2046,22 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENEL.MI</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9.859999999999999</v>
+        <v>608.36</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2069,11 +2069,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2097,34 +2097,34 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BESI</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>287.2</v>
+        <v>129.55</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2148,22 +2148,22 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DAN.MI</t>
+          <t>SHEN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>71.5</v>
+        <v>16.01</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2199,34 +2199,34 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OHB.DE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>583</v>
+        <v>17.57</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2250,22 +2250,22 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CABK.MC</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>117.51</v>
+        <v>11.62</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2301,30 +2301,30 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ELG.DE</t>
+          <t>OVS.MI</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>186.2</v>
+        <v>5.43</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2352,30 +2352,30 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RIO.L</t>
+          <t>ENR.DE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7941</v>
+        <v>181.04</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2403,39 +2403,39 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AIR</t>
+          <t>HOT.DE</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>112.93</v>
+        <v>486</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2454,30 +2454,30 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>232.1</v>
+        <v>193.78</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2505,39 +2505,39 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>309.3</v>
+        <v>431.54</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2556,39 +2556,39 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-05-26 16:07</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53.31</v>
+        <v>530.27</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2607,30 +2607,30 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22.04</v>
+        <v>94.47</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2658,39 +2658,39 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>205.64</v>
+        <v>22.4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2700,31 +2700,31 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0.13</v>
+        <v>6.05</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DOCN</t>
+          <t>EOSE</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>163.08</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2732,11 +2732,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2760,30 +2760,30 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29</v>
+        <v>432.51</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2811,22 +2811,22 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>BAM</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66.23999999999999</v>
+        <v>48.74</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2862,30 +2862,30 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>91.81999999999999</v>
+        <v>65.75</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2913,30 +2913,30 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
+          <t>2026-05-26 16:48</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>KODK</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>114.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2964,2204 +2964,11 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ANA.MC</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>260.4</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>40</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>REP.MC</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>40</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>ANE.MC</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>24.28</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>40</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ABBN.SW</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>84.86</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>COMPRA TEMPRANA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>40</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>489.56</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>40</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>INTC</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>121.64</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>40</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>267.43</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>40</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>210.05</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>40</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>DHI</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>145.77</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>40</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AMAT</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>447.69</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>40</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>857.12</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>40</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>QCOM</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>243.05</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>40</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>255.83</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>40</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>GNTX</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>24.08</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>COMPRA TEMPRANA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>40</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>609.71</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>40</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BABA</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>129.98</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>40</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>SHEN</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>40</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>AMPX</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>17.68</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>COMPRA TEMPRANA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>40</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MAP.MC</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>25</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>CBRS</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>240.71</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>25</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>CABK.MC</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>25</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>OVS.MI</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>25</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>ENR.DE</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>179.26</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>25</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>HOT.DE</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>485.8</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>25</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>ORCL</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>194.64</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>25</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>429.04</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>25</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>524</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>25</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>IGV</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>94.48999999999999</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>25</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>SPCX</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>25</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>DISTRIBUYENDO</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>MEL.MC</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>15</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>MVC.MC</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>COMPRA TEMPRANA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>15</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ITX.MC</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>15</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>OBDC</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>15</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>417.79</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>15</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>165.23</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>COMPRA TEMPRANA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>15</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>EOSE</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>15</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>429.17</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>15</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>BAM</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>48.81</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>ESPERA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>15</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>COMPRANDO</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>ASM</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>281.41</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>66.04000000000001</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>KODK</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>2026-05-26 16:09</t>
+          <t>2026-05-26 16:49</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1063.5</v>
+        <v>65</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -512,26 +512,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.24</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-22 16:16</t>
+          <t>2026-05-22 18:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>UFO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>268.08</v>
+        <v>61.42</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.12</v>
+        <v>1.47</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-22 16:16</t>
+          <t>2026-05-22 18:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>309.14</v>
+        <v>28.64</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -614,26 +614,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-22 16:16</t>
+          <t>2026-05-22 19:01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F8P</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.79</v>
+        <v>733.98</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,11 +669,7304 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-22 16:19</t>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FTAI</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>253.63</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HWM</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>258.32</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>406.87</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1643.01</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>65</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>308.98</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>267.67</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>307.74</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>198.01</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>313.25</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>358.05</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>112.53</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>65</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>65</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>65</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AES</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>65</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PNW</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>65</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EDF.PA</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>65</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VIE.PA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>65</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ORA.PA</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>65</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ORSTED.CO</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>167.45</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>65</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EBK</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>65</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>55</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SPCE</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>55</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>55</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SVT.L</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3128</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>55</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>133.42</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LUNR</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUVL</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>102.81</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EVRG</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>83.76000000000001</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ENEL.MI</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ENGI.PA</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>50</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ACE.MI</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>50</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RHM.DE</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1227.2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SAF</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>285</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IDR.MC</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TDG</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1213.77</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RCAT</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>204.57</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>40</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VSAT</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AIOT</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>40</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>IRDM</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>40</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GSAT</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>82.70999999999999</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>40</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>555.38</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>470.23</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>40</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>608.08</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>40</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>40</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>40</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>256.67</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AMWL</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>40</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>40</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>216.28</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>40</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OSCR</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>40</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LENZ</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>40</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ATRY.MC</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>40</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>HAE</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>40</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>436.24</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>378.86</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>40</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>121.01</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>40</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1901.27</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>40</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>40</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1585.96</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>40</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>769.96</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>40</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>40</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>40</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>530.98</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>40</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>40</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>314.88</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>40</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>295.9</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>40</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>131.11</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>40</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>68.18000000000001</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>40</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>XEL</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>80.92</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>40</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>108.12</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>40</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>79.73999999999999</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>40</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PCG</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>40</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>40</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>WEC</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>40</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>40</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>OGE</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>40</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EOAN</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>40</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SSE.L</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2427</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>40</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>UU.L</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>40</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>25</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>LDO.MI</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>52.32</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>25</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>25</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KTOS</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>25</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AVAV</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>170.91</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>25</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ONDS</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>25</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>LMT</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>529.6</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>25</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>217.07</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>25</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>413.74</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>25</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>385.89</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>25</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>192.4</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>25</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>137.01</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>25</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>180.1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>25</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>244.44</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>25</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>324.99</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>25</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PEGA</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>25</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TALK</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>25</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>VKTX</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>25</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TLX.DE</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>25</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CMPX</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>25</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>438.88</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>25</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>397.12</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>25</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>116.93</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>25</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>814.39</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>25</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>484.54</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>25</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DUK</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>125.47</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>25</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>25</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SRE</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>25</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>25</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>25</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>25</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CNP</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>25</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>RWE</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>25</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TRN.MI</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>25</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BA.</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>219.62</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>15</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>133.38</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>15</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CLFD</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>15</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>219.54</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>15</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>418.74</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>15</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>427.3</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>15</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>102.38</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>15</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>15</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ALUR</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>15</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LRMR</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>15</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MOH</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>181.26</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>15</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>15</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>NG.L</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>15</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SPAI</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>GILT</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>72.34999999999999</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HIMS</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>LFMD</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ALHC</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ABVC</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TYRA</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ASMB</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>GOSS</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>IBE.MC</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:02</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107.29</v>
+        <v>269.54</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.289999999999999</v>
+        <v>936</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -567,30 +567,30 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.75</v>
+        <v>0.36</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>310.19</v>
+        <v>232.59</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,22 +618,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.34</v>
+        <v>0.15</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-26 17:59</t>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CODX</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.35</v>
+        <v>66.64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -665,26 +665,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3.83</v>
+        <v>0.32</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-26 17:57</t>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PDYN</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.19</v>
+        <v>24.83</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -716,30 +716,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>QBTS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165.18</v>
+        <v>28.04</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -771,26 +771,26 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.93</v>
+        <v>0.45</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ARQQ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>521.38</v>
+        <v>16.72</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -822,62 +822,776 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-26 17:59</t>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>265.4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>424.11</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>506.76</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>448.17</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>315.11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1923.53</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>40</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QUBT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>VENTA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>389.54</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>370.58</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>196.11</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>118.52</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>212.56</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>VENDIENDO</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-05-26 17:57</t>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>485.15</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:32</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1018.87</v>
+        <v>233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -488,39 +488,1110 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>274</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>65</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>COMPRANDO</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>NEUTRO</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-05-21 12:46</t>
+      <c r="J3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>518.09</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>449.68</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>65</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>923.52</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RGTI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QUBT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QBTS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>264.22</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>55</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>426.99</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>55</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>204.83</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ARQQ</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>40</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>318</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1927.63</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>178.96</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>40</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>390.13</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>373.85</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>118.64</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>480.64</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:20</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>0IE9</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>233</v>
+        <v>24.15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.11</v>
+        <v>4.78</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>65</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>OVS.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>518.09</v>
+        <v>5.62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -618,22 +618,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>449.68</v>
+        <v>952.83</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.83</v>
+        <v>0.13</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>MTE.DE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>923.52</v>
+        <v>812.6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70.14</v>
+        <v>273.6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -767,38 +767,38 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.03</v>
+        <v>1120.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -818,38 +818,38 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2.27</v>
+        <v>0.05</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.24</v>
+        <v>314.42</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -869,38 +869,38 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.54</v>
+        <v>0.08</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QBTS</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.49</v>
+        <v>456.4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -920,38 +920,38 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1.64</v>
+        <v>0.06</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>264.22</v>
+        <v>42.17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -971,38 +971,38 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.78</v>
+        <v>0.43</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>426.99</v>
+        <v>159.05</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1022,34 +1022,34 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1.38</v>
+        <v>0.05</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>204.83</v>
+        <v>267.11</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1073,38 +1073,38 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1.92</v>
+        <v>0.09</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARQQ</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.91</v>
+        <v>350.59</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1128,30 +1128,30 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>0.13</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120.89</v>
+        <v>256.49</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1179,30 +1179,30 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.75</v>
+        <v>0.11</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ITX.MC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>318</v>
+        <v>53.8</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1230,30 +1230,30 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.87</v>
+        <v>0.23</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NHY.OL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1927.63</v>
+        <v>113.3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1281,34 +1281,34 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0.26</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>URW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>178.96</v>
+        <v>99.14</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1332,30 +1332,30 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1.11</v>
+        <v>0.1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CGEO.L</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>390.13</v>
+        <v>4200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1383,30 +1383,30 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>214.25</v>
+        <v>82.39</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1434,34 +1434,34 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373.85</v>
+        <v>232.16</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1485,30 +1485,30 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.83</v>
+        <v>0.08</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>OHLA.MC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>118.64</v>
+        <v>0.49</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1536,62 +1536,7508 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.87</v>
+        <v>0.44</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 15:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>F8P</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>480.64</v>
+        <v>55.96</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>65</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1B8</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>65</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3ZU0</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>65</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ACX.MC</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>65</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IDR.MC</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>65</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>65</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FTAI</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>259.33</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>65</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>110.32</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>65</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VSAT</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>65</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ONDS</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UFO</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>63.65</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>65</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>46.74</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>65</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RDW</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>65</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VOYG</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>65</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NXT</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>155.58</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>65</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PLUG</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>65</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1SOFI.MI</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>VENTA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D39" t="n">
+        <v>55</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WF5A</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>55</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DAN.MI</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>50</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FER.MC</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>749.9299999999999</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>50</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ANA.MC</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GRF.MC</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>40</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1643.61</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>40</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ABBN.SW</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>40</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AZM.MI</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>628.6900000000001</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>40</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DHI</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>147.04</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>40</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>311.54</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>40</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GNTX</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>40</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BAM</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EOSE</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>40</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>124.88</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>40</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>520.03</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>40</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AMPX</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>40</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>202.99</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>40</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>40</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MVC.MC</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>40</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ELG.DE</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>180</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>114.49</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>40</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>40</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>INGA</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>40</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LUNR</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>40</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SATL</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>40</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SYM</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>40</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DOCN</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>152.01</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>40</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>366.65</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>40</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>40</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>439.37</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>40</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>135.56</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>40</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>226.78</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>40</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MTS.MC</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>40</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SAN.MC</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>40</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>YDX</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>195.08</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>40</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SAP.DE</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>151.18</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>40</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>40</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>RQ0</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>40</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BBAI</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>40</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>40</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>40</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>40</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>RHM.DE</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1293.3</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>40</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>LDO.MI</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>40</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BA.</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>40</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TDG</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1253.66</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>40</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>176.76</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>40</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>KTOS</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>40</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AVAV</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>40</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>RCAT</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>40</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>139.06</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>40</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>HWM</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>258.08</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>40</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SPAI</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>40</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>GSAT</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>83.59</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>40</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SPCE</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>40</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>555.49</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>40</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MNTS</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>40</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>426.7</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>40</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>320.07</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>40</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ESLT</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>872.3200000000001</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>40</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>314.49</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>40</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CABK.MC</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>25</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LOG.MC</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>25</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>25</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>HOT.DE</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>484</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>25</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>OHB.DE</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>460.5</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>25</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>533.52</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>25</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>118.89</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>25</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>439.51</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>25</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IGV</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>25</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>214.55</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>25</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>25</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UNI.MC</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>25</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SAB.MC</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>25</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>BKT.MC</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>25</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>GRE.MC</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>25</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>RIO.L</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>7948</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>25</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>131.84</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>25</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>198.84</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>25</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CBRS</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>245.2</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>25</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NVD.DE</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>184.44</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>25</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>82W</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>25</v>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
         <is>
           <t>VENDIENDO</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FB2A.DE</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>542.8</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>25</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>184.04</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>25</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>25</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SAF</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>307.3</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>25</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>LMT</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>531.45</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>25</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AIOT</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>25</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>IRDM</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>25</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FLY</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>25</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BBD.A</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>25</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CLPS</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>25</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>REP.MC</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>15</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ANE.MC</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>15</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>438.47</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>15</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SHEN</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>15</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MEL.MC</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>15</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>15</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>15</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>OBDC</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>15</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>15</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>15</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>3UX</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>15</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TGTX</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>15</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>KODK</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SCYR.MC</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>MAP.MC</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ENEL.MI</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>296.87</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CCI</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>NFC</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>132.44</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ENR.DE</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>163.48</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ENGI</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>IBE.MC</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ACS.MC</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>5R02</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
         <is>
           <t>DISTRIBUYENDO</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-05-29 12:20</t>
+      <c r="J166" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SOBA</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>108.12</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AIR.MC</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:43</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>SAN.MC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107.29</v>
+        <v>10.86</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.34</v>
+        <v>0.68</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-27 18:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>ACX.MC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.289999999999999</v>
+        <v>15.87</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.75</v>
+        <v>0.57</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-27 18:47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AZM.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>310.19</v>
+        <v>35.34</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -618,34 +618,34 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-26 17:59</t>
+          <t>2026-05-27 18:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CODX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.35</v>
+        <v>1601.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,38 +665,38 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3.83</v>
+        <v>0.51</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-26 17:57</t>
+          <t>2026-05-27 18:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PDYN</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.19</v>
+        <v>271.84</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -716,38 +716,38 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.47</v>
+        <v>0.46</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-27 18:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165.18</v>
+        <v>29.86</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -771,34 +771,34 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.93</v>
+        <v>0.72</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-26 17:58</t>
+          <t>2026-05-27 18:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>521.38</v>
+        <v>155.26</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -822,62 +822,3479 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-26 17:59</t>
+          <t>2026-05-27 18:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>37.04</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>65</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>230.07</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>307.13</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1083.7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NHY.OL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CGEO.L</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4055</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INGA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0IE9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>65</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>128.27</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>65</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ITX.MC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>53</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COMPRA FUERTE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>65</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LUNR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>VENTA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D20" t="n">
+        <v>55</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOG.MC</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DAN.MI</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>310.67</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SCYR.MC</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BKT.MC</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MTS.MC</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>40</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ABBN.SW</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IFX.DE</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>76.73</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>119.74</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>40</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SHEN</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>495.33</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>40</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>613.24</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>40</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AMPX</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DHI</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>147.11</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>249.34</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>40</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ELG.DE</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>184</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>40</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>URW</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>113.18</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>303.21</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DOCN</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>152.95</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>40</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CABK.MC</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>25</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>25</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OVS.MI</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>25</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>534.47</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>25</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>201.75</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>25</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>421.54</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>25</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SAB.MC</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>25</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>UNI.MC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>25</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RIO.L</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7908</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>25</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>25</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SYM</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>25</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>REP.MC</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ANA.MC</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>251</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ANE.MC</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MEL.MC</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MVC.MC</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>OBDC</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>297.17</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>15</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>155.83</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>15</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>413.77</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>15</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>441.76</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>15</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ACS.MC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>126</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>VENDIENDO</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-05-26 17:57</t>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HOT.DE</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ENR.DE</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>174.36</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>64.36</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>189.78</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>KODK</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MAP.MC</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>GRE.MC</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>120</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ENEL.MI</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:49</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>233</v>
+        <v>133.09</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>65</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>518.09</v>
+        <v>13.25</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -614,26 +614,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.79</v>
+        <v>3.56</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>UFO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>449.68</v>
+        <v>67.81</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -665,26 +665,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.83</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>RDW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>923.52</v>
+        <v>25.9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -716,38 +716,38 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.98</v>
+        <v>2.54</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>VOYG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70.14</v>
+        <v>51.77</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -771,34 +771,34 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>IDR.MC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.03</v>
+        <v>56.12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -818,38 +818,38 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2.27</v>
+        <v>0.31</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.24</v>
+        <v>3.93</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -869,38 +869,38 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QBTS</t>
+          <t>FTAI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.49</v>
+        <v>262.78</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -920,38 +920,38 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>264.22</v>
+        <v>86.69</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -971,38 +971,38 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>426.99</v>
+        <v>51.4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1022,34 +1022,34 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1.38</v>
+        <v>0.73</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>204.83</v>
+        <v>137.17</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1073,38 +1073,38 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1.92</v>
+        <v>0.66</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARQQ</t>
+          <t>PLUG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.91</v>
+        <v>4.12</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1128,39 +1128,39 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>1.15</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120.89</v>
+        <v>1265.06</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1175,26 +1175,26 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>KTOS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>318</v>
+        <v>65.19</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.87</v>
+        <v>2.69</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1927.63</v>
+        <v>214.39</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1253,16 +1253,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1277,34 +1277,34 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>3.39</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>RCAT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>178.96</v>
+        <v>14.15</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1328,43 +1328,43 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1.11</v>
+        <v>5.51</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SPAI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>390.13</v>
+        <v>5.41</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1374,39 +1374,39 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.86</v>
+        <v>3.37</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>LUNR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>214.25</v>
+        <v>45.7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1425,39 +1425,39 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.89</v>
+        <v>1.48</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SPCE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373.85</v>
+        <v>4.53</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1476,48 +1476,48 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.83</v>
+        <v>3.64</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>118.64</v>
+        <v>559.29</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1527,71 +1527,1346 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.87</v>
+        <v>1.33</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-05-29 12:20</t>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>MNTS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>480.64</v>
+        <v>19.4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>55</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>439.32</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>VENTA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" t="n">
+        <v>55</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ESLT</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>892.63</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>55</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>55</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>747.73</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RHM.DE</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1288.4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LDO.MI</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>40</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BA.</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>228.78</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>178.96</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>40</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>148.03</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>40</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HWM</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>259.89</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GSAT</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>228.78</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>40</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EOSE</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>40</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>320.82</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>320.9</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SAF</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>25</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LMT</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>537.21</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>25</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AIOT</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>25</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IRDM</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>25</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FLY</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>25</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BBD.A</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>25</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CLPS</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>25</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AIR.MC</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>180.96</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>VENDIENDO</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>DISTRIBUYENDO</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-05-29 12:20</t>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:13</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>133.09</v>
+        <v>971</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>120.42</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.25</v>
+        <v>446.77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -618,22 +618,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3.56</v>
+        <v>1.92</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UFO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.81</v>
+        <v>159.47</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RDW</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.9</v>
+        <v>281.69</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VOYG</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51.77</v>
+        <v>747.61</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.98</v>
+        <v>3.19</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IDR.MC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56.12</v>
+        <v>65</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.31</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.93</v>
+        <v>80.62</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -869,26 +869,26 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.28</v>
+        <v>2.5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FTAI</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>262.78</v>
+        <v>13.22</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -920,26 +920,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>IRDM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86.69</v>
+        <v>51.78</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -971,26 +971,26 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UFO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51.4</v>
+        <v>65.31</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1022,26 +1022,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.73</v>
+        <v>3.59</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>137.17</v>
+        <v>51.14</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1073,26 +1073,26 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLUG</t>
+          <t>RDW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.12</v>
+        <v>24.57</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1124,38 +1124,38 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1.15</v>
+        <v>1.84</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>VOYG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1265.06</v>
+        <v>49.53</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1179,34 +1179,34 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KTOS</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>65.19</v>
+        <v>236.03</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1230,34 +1230,34 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2.69</v>
+        <v>1.12</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>214.39</v>
+        <v>137.97</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1281,34 +1281,34 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3.39</v>
+        <v>1.53</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RCAT</t>
+          <t>DAN.MI</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.15</v>
+        <v>74.55</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1328,38 +1328,38 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5.51</v>
+        <v>0.62</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SPAI</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.41</v>
+        <v>113.41</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1379,34 +1379,34 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3.37</v>
+        <v>2.73</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>MTE.DE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>45.7</v>
+        <v>873.3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1430,38 +1430,38 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1.48</v>
+        <v>0.44</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SPCE</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.53</v>
+        <v>1105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1481,38 +1481,38 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3.64</v>
+        <v>1.44</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>559.29</v>
+        <v>312.06</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1532,38 +1532,38 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MNTS</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.4</v>
+        <v>43.04</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1583,38 +1583,38 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2.7</v>
+        <v>4.62</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>439.32</v>
+        <v>353.29</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1634,38 +1634,38 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1.52</v>
+        <v>0.98</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-05-29 13:14</t>
+          <t>2026-06-01 12:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>OHLA.MC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>892.63</v>
+        <v>0.48</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1685,38 +1685,38 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>0.29</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-05-29 13:14</t>
+          <t>2026-06-01 12:28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>1B8</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48.68</v>
+        <v>11.24</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1736,34 +1736,34 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2.11</v>
+        <v>0.52</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-05-29 13:14</t>
+          <t>2026-06-01 12:29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>F8P</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>747.73</v>
+        <v>54.33</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1791,34 +1791,34 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RHM.DE</t>
+          <t>IDR.MC</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1288.4</v>
+        <v>56.98</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1842,34 +1842,34 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HO</t>
+          <t>FTAI</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>239.9</v>
+        <v>260.34</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1893,34 +1893,34 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.17</v>
+        <v>1.18</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LDO.MI</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54.41</v>
+        <v>156.4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1944,34 +1944,34 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.25</v>
+        <v>2.04</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:32</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BA.</t>
+          <t>PLUG</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>228.78</v>
+        <v>3.95</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1995,34 +1995,34 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:32</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>BKT.MC</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>178.96</v>
+        <v>14.44</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2046,30 +2046,30 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>0IE9</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>148.03</v>
+        <v>23.37</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2093,34 +2093,34 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.77</v>
+        <v>1.22</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>URW</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>259.89</v>
+        <v>99.62</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2148,30 +2148,30 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.89</v>
+        <v>0.13</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>CGEO.L</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84.43000000000001</v>
+        <v>4210</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2199,34 +2199,34 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>228.78</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2250,30 +2250,30 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.95</v>
+        <v>0.29</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:34</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EOSE</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.99</v>
+        <v>101.66</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2297,34 +2297,34 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.62</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>320.82</v>
+        <v>225.78</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2348,26 +2348,26 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.83</v>
+        <v>1.6</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-05-29 13:14</t>
+          <t>2026-06-01 12:25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>320.9</v>
+        <v>205</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2375,16 +2375,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2399,43 +2399,43 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-05-29 13:14</t>
+          <t>2026-06-01 12:26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAF</t>
+          <t>YDX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>308.1</v>
+        <v>212</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2445,39 +2445,39 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.25</v>
+        <v>2.7</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>537.21</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2496,39 +2496,39 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.77</v>
+        <v>1.97</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AIOT</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.61</v>
+        <v>9</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2547,48 +2547,48 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.84</v>
+        <v>1.47</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IRDM</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>51.26</v>
+        <v>12.67</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2598,48 +2598,48 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0.77</v>
+        <v>1.38</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FLY</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>49.37</v>
+        <v>189.03</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2649,39 +2649,39 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>2.02</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-05-29 13:13</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BBD.A</t>
+          <t>BA.</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.52</v>
+        <v>231.15</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2700,39 +2700,39 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-05-29 13:14</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CLPS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.88</v>
+        <v>179.66</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2751,31 +2751,31 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0.47</v>
+        <v>1.63</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-05-29 13:14</t>
+          <t>2026-06-01 12:30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RCAT</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.16</v>
+        <v>14.5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2807,66 +2807,7104 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0.88</v>
+        <v>2.59</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-05-29 13:12</t>
+          <t>2026-06-01 12:31</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>143.48</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>55</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SPAI</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>55</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LUNR</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>55</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AIOT</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>55</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>231.15</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>55</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SPCE</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>55</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>563.6799999999999</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>55</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FLY</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>55</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>448.72</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>55</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>55</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>450.24</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>55</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>156.54</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>55</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>255.55</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>55</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>55</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>124.37</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>55</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>259.21</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>55</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PEGA</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>55</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>297.8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>55</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>55</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>OBDC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>55</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CCI</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>55</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>159.09</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>55</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>270.64</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>50</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>251.02</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>50</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>20</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>50</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>50</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NHY.OL</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>50</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>RIO.L</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>8033</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>50</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>REP.MC</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>40</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1612.76</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>40</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ABBN.SW</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>40</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>HOT.DE</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>489.2</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>40</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>149.25</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>40</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AZM.MI</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>40</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>632.51</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>40</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>306.79</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>40</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BAM</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>40</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>124.22</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>40</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>40</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AMPX</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>40</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>44.73</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>40</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MTS.MC</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>40</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SAP.DE</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>160.84</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>40</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>RQ0</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>40</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>40</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BBAI</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>40</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>40</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ACX.MC</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>40</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>RHM.DE</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1253.2</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>40</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>LDO.MI</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>40</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TDG</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1258.32</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>40</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>40</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>KTOS</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>40</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AVAV</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>207.24</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>40</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HWM</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>40</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>GSAT</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>40</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MNTS</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>40</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ESLT</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>880.89</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>40</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>418.45</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>40</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>40</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>40</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>UNI.MC</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>40</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MVC.MC</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>40</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SCYR.MC</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>40</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>112.62</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>40</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SATL</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>40</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DOCN</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>155.95</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>40</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>40</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>135.53</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>40</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1SOFI.MI</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>40</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>299.31</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>30</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>30</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>139.73</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>30</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CABK.MC</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>25</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>LOG.MC</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>25</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>25</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>OVS.MI</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>25</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DHI</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>147.09</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>25</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>531.21</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>25</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GNTX</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>25</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>114.68</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>25</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>450.06</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>25</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>25</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SAN.MC</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>25</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FER.MC</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>25</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>82W</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>25</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NVD.DE</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>184.64</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>25</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>3ZU0</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>25</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>25</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SAF</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>25</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>LMT</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>530.45</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>25</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BBD.A</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>25</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CLPS</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>25</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>25</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SAB.MC</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>25</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ITX.MC</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>25</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>GRE.MC</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>126</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>25</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>INGA</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>25</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CBRS</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>236.99</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>25</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ANE.MC</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>15</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>435.79</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>15</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SHEN</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>15</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>87.01000000000001</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>15</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>EOSE</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>15</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>IBE.MC</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>15</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>3UX</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>15</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TGTX</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>15</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>15</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MEL.MC</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>15</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ELG.DE</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>15</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>15</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ANA.MC</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>249.2</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>GRF.MC</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>62.36</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>KODK</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>OHB.DE</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>447</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ACS.MC</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ENGI</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>WF5A</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>FB2A.DE</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SOBA</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>109.82</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>5R02</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>AIR.MC</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>180.96</v>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B173" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>VENTA</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D173" t="n">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
         <is>
           <t>VENDIENDO</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2026-05-29 13:13</t>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>308.17</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>211.14</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>380.34</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>MAP.MC</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ENEL.MI</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SYM</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>277.4</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>195.88</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>NFC</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ENR.DE</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>164.18</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>154.75</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:34</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K186"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>971</v>
+        <v>459.97</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120.42</v>
+        <v>47</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.75</v>
+        <v>5.33</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>446.77</v>
+        <v>170.68</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -618,22 +618,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>159.47</v>
+        <v>300.48</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>281.69</v>
+        <v>21.75</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.85</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>747.61</v>
+        <v>219.43</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3.19</v>
+        <v>1.17</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>408.85</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>F8P</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.62</v>
+        <v>56.17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.22</v>
+        <v>65</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -924,22 +924,22 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IRDM</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51.78</v>
+        <v>147.14</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UFO</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65.31</v>
+        <v>414.16</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1026,22 +1026,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3.59</v>
+        <v>1.88</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>AZM.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51.14</v>
+        <v>35.02</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1073,26 +1073,26 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RDW</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24.57</v>
+        <v>105.65</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1124,26 +1124,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1.84</v>
+        <v>1.33</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VOYG</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49.53</v>
+        <v>1035.5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1175,26 +1175,26 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1.54</v>
+        <v>0.93</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>MTE.DE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>236.03</v>
+        <v>882.7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1.12</v>
+        <v>0.21</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>SHEN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>137.97</v>
+        <v>16.19</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1277,26 +1277,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1.53</v>
+        <v>0.93</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DAN.MI</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>74.55</v>
+        <v>121.33</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1332,22 +1332,22 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.62</v>
+        <v>0.99</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>OHLA.MC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>113.41</v>
+        <v>0.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2.73</v>
+        <v>0.22</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MTE.DE</t>
+          <t>YDX</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>873.3</v>
+        <v>233.95</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1434,22 +1434,22 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>1B8</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1105</v>
+        <v>11.44</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1481,26 +1481,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1.44</v>
+        <v>0.12</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVD.DE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>312.06</v>
+        <v>195</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1.52</v>
+        <v>0.55</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>IDR.MC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>43.04</v>
+        <v>55.04</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4.62</v>
+        <v>0.25</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>353.29</v>
+        <v>13.46</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.98</v>
+        <v>1.23</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OHLA.MC</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.48</v>
+        <v>46.46</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1689,22 +1689,22 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.29</v>
+        <v>0.98</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1B8</t>
+          <t>RDW</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.24</v>
+        <v>20.68</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1736,26 +1736,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.52</v>
+        <v>1.58</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>F8P</t>
+          <t>VOYG</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54.33</v>
+        <v>47.49</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1791,22 +1791,22 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.66</v>
+        <v>1.25</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IDR.MC</t>
+          <t>PLUG</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>56.98</v>
+        <v>3.94</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1842,22 +1842,22 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FTAI</t>
+          <t>URW</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>260.34</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1893,34 +1893,34 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1.18</v>
+        <v>0.08</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>156.4</v>
+        <v>303</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1940,38 +1940,38 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PLUG</t>
+          <t>GNTX</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.95</v>
+        <v>24.08</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1991,38 +1991,38 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BKT.MC</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14.44</v>
+        <v>107.7</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2042,38 +2042,38 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0IE9</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.37</v>
+        <v>248.15</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2093,38 +2093,38 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1.22</v>
+        <v>1.84</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>URW</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>99.62</v>
+        <v>8.74</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2144,38 +2144,38 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.13</v>
+        <v>1.23</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CGEO.L</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4210</v>
+        <v>9.25</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2195,38 +2195,38 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.23</v>
+        <v>1.23</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>83.45999999999999</v>
+        <v>12.89</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2246,30 +2246,30 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.29</v>
+        <v>1.27</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>101.66</v>
+        <v>5.34</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2301,26 +2301,26 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>225.78</v>
+        <v>255.52</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2352,22 +2352,22 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>205</v>
+        <v>476.88</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2403,22 +2403,22 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>YDX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>212</v>
+        <v>160.65</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2454,26 +2454,26 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2.7</v>
+        <v>1.23</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8.380000000000001</v>
+        <v>280.16</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2505,26 +2505,26 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>209.6</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2556,26 +2556,26 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12.67</v>
+        <v>274.03</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2607,26 +2607,26 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>189.03</v>
+        <v>403.88</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2658,26 +2658,26 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BA.</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>231.15</v>
+        <v>11.75</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2709,22 +2709,22 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1.01</v>
+        <v>2.29</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>179.66</v>
+        <v>23.22</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2760,22 +2760,22 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RCAT</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14.5</v>
+        <v>48.4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2811,26 +2811,26 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>DOCN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>143.48</v>
+        <v>173.45</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SPAI</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6.15</v>
+        <v>30.59</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2913,26 +2913,26 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>2.84</v>
+        <v>1.37</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>43.83</v>
+        <v>5.51</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2964,26 +2964,26 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AIOT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.91</v>
+        <v>135.98</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -3015,26 +3015,26 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>2.86</v>
+        <v>1.2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>231.15</v>
+        <v>91.03</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3066,26 +3066,26 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SPCE</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6.18</v>
+        <v>155.71</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3117,34 +3117,34 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>11.98</v>
+        <v>2.37</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>OVS.MI</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>563.6799999999999</v>
+        <v>5.91</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3159,39 +3159,39 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>2.39</v>
+        <v>0.63</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FLY</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>46.49</v>
+        <v>458.17</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3210,43 +3210,43 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>2.83</v>
+        <v>0.96</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>448.72</v>
+        <v>228.99</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3261,31 +3261,31 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1.29</v>
+        <v>0.96</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>323.76</v>
+        <v>435.63</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3293,11 +3293,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3312,43 +3312,43 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>450.24</v>
+        <v>7.29</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3363,43 +3363,43 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2.26</v>
+        <v>0.67</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NHY.OL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>156.54</v>
+        <v>119.25</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3414,31 +3414,31 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>0.14</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>255.55</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3446,11 +3446,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3465,31 +3465,31 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>2.36</v>
+        <v>0.28</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>191.1</v>
+        <v>21.8</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3497,11 +3497,11 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3516,31 +3516,31 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>2.47</v>
+        <v>0.89</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>124.37</v>
+        <v>317.12</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3548,11 +3548,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3567,39 +3567,39 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>2.51</v>
+        <v>0.84</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>REP.MC</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>259.21</v>
+        <v>22.35</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3623,43 +3623,43 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>2.13</v>
+        <v>0.05</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.73</v>
+        <v>1628.57</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3674,43 +3674,43 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1.46</v>
+        <v>0.61</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>ABBN.SW</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>297.8</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3725,43 +3725,43 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>3.91</v>
+        <v>0.11</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>DAN.MI</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>29.03</v>
+        <v>72.8</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3776,26 +3776,26 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1.49</v>
+        <v>0.18</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OBDC</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>11.26</v>
+        <v>1082.2</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3803,16 +3803,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3827,34 +3827,34 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1.25</v>
+        <v>0.84</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>91.5</v>
+        <v>125.4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3878,34 +3878,34 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1.62</v>
+        <v>0.84</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>EOSE</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>159.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3929,26 +3929,26 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>270.64</v>
+        <v>510.13</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3975,31 +3975,31 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MTS.MC</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>251.02</v>
+        <v>61.08</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4035,34 +4035,34 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>1.33</v>
+        <v>0.2</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>20</v>
+        <v>171.52</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4086,34 +4086,34 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>RQ0</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7.32</v>
+        <v>25.4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4137,22 +4137,22 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NHY.OL</t>
+          <t>3ZU0</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>115.3</v>
+        <v>93.2</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4188,22 +4188,22 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RIO.L</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>8033</v>
+        <v>46.88</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4211,11 +4211,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4239,34 +4239,34 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0.15</v>
+        <v>1.11</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21.76</v>
+        <v>182.61</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4281,31 +4281,31 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>REP.MC</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22.28</v>
+        <v>27.51</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4341,22 +4341,22 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.08</v>
+        <v>0.8</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ACX.MC</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1612.76</v>
+        <v>15.68</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4392,26 +4392,26 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.61</v>
+        <v>0.16</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ABBN.SW</t>
+          <t>LDO.MI</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>84.16</v>
+        <v>51.6</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HOT.DE</t>
+          <t>BA.</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>489.2</v>
+        <v>224.3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4494,26 +4494,26 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>149.25</v>
+        <v>719.99</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4541,30 +4541,30 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.22</v>
+        <v>1.18</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AZM.MI</t>
+          <t>FTAI</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>34.64</v>
+        <v>247.82</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4596,26 +4596,26 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>0.11</v>
+        <v>0.58</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>632.51</v>
+        <v>174.41</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -4643,26 +4643,26 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KTOS</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>306.79</v>
+        <v>63.49</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4698,22 +4698,22 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>2.43</v>
+        <v>1.43</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BAM</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>48.6</v>
+        <v>204.09</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4753,18 +4753,18 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>RCAT</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>124.22</v>
+        <v>14.84</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4800,26 +4800,26 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>1.08</v>
+        <v>1.93</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>516.1</v>
+        <v>122.39</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4847,26 +4847,26 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>0.78</v>
+        <v>1.38</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>SPAI</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>20.28</v>
+        <v>6.22</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>0.97</v>
+        <v>1.21</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>LUNR</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>44.73</v>
+        <v>38.21</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4949,26 +4949,26 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>2.44</v>
+        <v>0.97</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MTS.MC</t>
+          <t>AIOT</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>59.82</v>
+        <v>3.93</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5000,26 +5000,26 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>0.18</v>
+        <v>1.2</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>GSAT</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>160.84</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5055,26 +5055,26 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>0.3</v>
+        <v>0.62</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>RQ0</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>25.65</v>
+        <v>224.3</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -5106,22 +5106,22 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>0.29</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SPCE</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>46.09</v>
+        <v>7.52</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5157,26 +5157,26 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>2.1</v>
+        <v>13.92</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>UFO</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>5.04</v>
+        <v>61.08</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5204,30 +5204,30 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>FLY</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>28.06</v>
+        <v>44.24</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5259,22 +5259,22 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ACX.MC</t>
+          <t>MNTS</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>15.76</v>
+        <v>16.71</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5310,22 +5310,22 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>0.19</v>
+        <v>0.97</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RHM.DE</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1253.2</v>
+        <v>324.6</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5361,22 +5361,22 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>0.31</v>
+        <v>0.75</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LDO.MI</t>
+          <t>ESLT</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>53.73</v>
+        <v>858.0599999999999</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5412,26 +5412,26 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1258.32</v>
+        <v>224.36</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5454,35 +5454,35 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>0.96</v>
+        <v>1.29</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3.89</v>
+        <v>460.52</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5510,30 +5510,30 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>0.45</v>
+        <v>1.49</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KTOS</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>64.13</v>
+        <v>135.86</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -5565,26 +5565,26 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>207.24</v>
+        <v>37.93</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -5616,22 +5616,22 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>2.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>258.25</v>
+        <v>320.42</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5643,12 +5643,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5667,22 +5667,22 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>2.81</v>
+        <v>4.18</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>84.20999999999999</v>
+        <v>69.28</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5718,22 +5718,22 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MNTS</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>16.85</v>
+        <v>73.77</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5760,35 +5760,35 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>UNI.MC</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>880.89</v>
+        <v>2.84</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5820,22 +5820,22 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>1.11</v>
+        <v>0.14</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BKT.MC</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>418.45</v>
+        <v>14.27</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5871,22 +5871,22 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>0.83</v>
+        <v>0.04</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>MVC.MC</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>10.77</v>
+        <v>10.44</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5922,26 +5922,26 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>2.27</v>
+        <v>0.1</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>0IE9</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>72.06999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -5969,26 +5969,26 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UNI.MC</t>
+          <t>AIR</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2.88</v>
+        <v>109.99</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6024,22 +6024,22 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>0.15</v>
+        <v>0.77</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MVC.MC</t>
+          <t>RIO.L</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>10.62</v>
+        <v>8201</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6075,22 +6075,22 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SCYR.MC</t>
+          <t>CGEO.L</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>4.68</v>
+        <v>4160</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -6126,26 +6126,26 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AIR</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>112.62</v>
+        <v>362.9</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6177,26 +6177,26 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SATL</t>
+          <t>OBDC</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>9.51</v>
+        <v>11.42</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6228,26 +6228,26 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DOCN</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>155.95</v>
+        <v>149.78</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6279,22 +6279,22 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>0.66</v>
+        <v>1.01</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>361.47</v>
+        <v>492.29</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -6302,11 +6302,11 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6326,43 +6326,43 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CABK.MC</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>135.53</v>
+        <v>11.67</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6381,39 +6381,39 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>2.24</v>
+        <v>0.06</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1SOFI.MI</t>
+          <t>BESI</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>15.98</v>
+        <v>278.2</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6423,39 +6423,39 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>1.33</v>
+        <v>0.14</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>299.31</v>
+        <v>146.98</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6474,43 +6474,43 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>1.54</v>
+        <v>0.79</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5.21</v>
+        <v>546.2</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6525,31 +6525,31 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>1.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>139.73</v>
+        <v>306.31</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6557,11 +6557,11 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6576,31 +6576,31 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>2.62</v>
+        <v>1.05</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CABK.MC</t>
+          <t>BAM</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>11.69</v>
+        <v>48.14</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6612,12 +6612,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6636,22 +6636,22 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LOG.MC</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>33.34</v>
+        <v>24.86</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6687,22 +6687,22 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>0.17</v>
+        <v>0.78</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BESI</t>
+          <t>ENGI</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>284.4</v>
+        <v>26.62</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6714,12 +6714,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6738,22 +6738,22 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OVS.MI</t>
+          <t>SAN.MC</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5.64</v>
+        <v>10.71</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6789,22 +6789,22 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>FER.MC</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>147.09</v>
+        <v>57.22</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6836,26 +6836,26 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>2.22</v>
+        <v>0.09</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>82W</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>531.21</v>
+        <v>23.66</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -6891,22 +6891,22 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>1.08</v>
+        <v>0.04</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GNTX</t>
+          <t>RHM.DE</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>24.16</v>
+        <v>1166.2</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6942,22 +6942,22 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>1.3</v>
+        <v>0.35</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>114.68</v>
+        <v>228.8</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6969,12 +6969,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -6989,26 +6989,26 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1.46</v>
+        <v>0.13</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>450.06</v>
+        <v>1238.41</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -7020,12 +7020,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7044,22 +7044,22 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>26.6</v>
+        <v>3.5</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -7095,22 +7095,22 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SAN.MC</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>10.73</v>
+        <v>516.5</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7146,22 +7146,22 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>0.12</v>
+        <v>0.92</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FER.MC</t>
+          <t>IRDM</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>58.22</v>
+        <v>47.81</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -7173,12 +7173,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7193,26 +7193,26 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>0.1</v>
+        <v>1.06</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>82W</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>22.4</v>
+        <v>145.02</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -7244,26 +7244,26 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>0.02</v>
+        <v>1.13</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NVD.DE</t>
+          <t>BBD.A</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>184.64</v>
+        <v>3.47</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7299,22 +7299,22 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3ZU0</t>
+          <t>CLPS</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>93.59999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -7326,12 +7326,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -7350,22 +7350,22 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>0.34</v>
+        <v>0.79</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>HO</t>
+          <t>ITX.MC</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>236.8</v>
+        <v>53.44</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -7401,22 +7401,22 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SAF</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>303.1</v>
+        <v>20</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -7452,22 +7452,22 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>530.45</v>
+        <v>26.62</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -7479,12 +7479,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -7499,26 +7499,26 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>1.51</v>
+        <v>0.11</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-06-01 12:31</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BBD.A</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3.49</v>
+        <v>226.1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -7550,30 +7550,30 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>0.67</v>
+        <v>1.86</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CLPS</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.9</v>
+        <v>213.28</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -7601,26 +7601,26 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>1SOFI.MI</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>21.56</v>
+        <v>15.87</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7652,26 +7652,26 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SAB.MC</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2.87</v>
+        <v>1940.04</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7707,22 +7707,22 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ITX.MC</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>53.46</v>
+        <v>311.38</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7758,22 +7758,22 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>0.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GRE.MC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>126</v>
+        <v>120.92</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7809,22 +7809,22 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>0.31</v>
+        <v>0.82</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>26.57</v>
+        <v>99.97</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7860,26 +7860,26 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>0.17</v>
+        <v>0.93</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>236.99</v>
+        <v>921.26</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -7887,12 +7887,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -7911,22 +7911,22 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ANE.MC</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>23.2</v>
+        <v>369.47</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7934,11 +7934,11 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7962,26 +7962,26 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>0.12</v>
+        <v>0.7</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ANE.MC</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>435.79</v>
+        <v>22.9</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -8013,26 +8013,26 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>0.74</v>
+        <v>0.05</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SHEN</t>
+          <t>HOT.DE</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>15.95</v>
+        <v>476.4</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -8064,26 +8064,26 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>1.61</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>87.01000000000001</v>
+        <v>415.88</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -8115,26 +8115,26 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>2.39</v>
+        <v>0.73</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EOSE</t>
+          <t>IBE.MC</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>8.43</v>
+        <v>19.47</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -8166,22 +8166,22 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-06-01 12:26</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IBE.MC</t>
+          <t>3UX</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>19.5</v>
+        <v>16.24</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -8217,22 +8217,22 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:12</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3UX</t>
+          <t>TGTX</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>15.5</v>
+        <v>37.41</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -8268,26 +8268,26 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>0.18</v>
+        <v>0.82</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TGTX</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>37.94</v>
+        <v>539.22</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -8315,30 +8315,30 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>0.6</v>
+        <v>1.58</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>SCYR.MC</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>335.55</v>
+        <v>4.59</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -8370,11 +8370,11 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>5.28</v>
+        <v>0.1</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>11.16</v>
+        <v>11.21</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -8421,11 +8421,11 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>178.8</v>
+        <v>177.6</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -8472,26 +8472,26 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SATL</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>44.75</v>
+        <v>8.67</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -8523,30 +8523,30 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>1.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:16</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ANA.MC</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>249.2</v>
+        <v>296.58</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8574,30 +8574,30 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>0.4</v>
+        <v>0.88</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GRF.MC</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>9.32</v>
+        <v>45.19</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8625,22 +8625,22 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.17</v>
+        <v>1.08</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-06-01 12:24</t>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>ANA.MC</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>62.36</v>
+        <v>246.6</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8676,22 +8676,22 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>0.9</v>
+        <v>0.08</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>KODK</t>
+          <t>LOG.MC</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>9.92</v>
+        <v>32.86</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8727,22 +8727,22 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>1.26</v>
+        <v>0.17</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OHB.DE</t>
+          <t>GRF.MC</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>447</v>
+        <v>9.17</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8778,22 +8778,22 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-06-01 12:25</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ACS.MC</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>125.3</v>
+        <v>148.3</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8829,22 +8829,22 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:02</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ENGI</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>26.81</v>
+        <v>63.76</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -8880,22 +8880,22 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>0.1</v>
+        <v>0.97</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>WF5A</t>
+          <t>KODK</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>57.66</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -8931,22 +8931,22 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-06-01 12:28</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FB2A.DE</t>
+          <t>OHB.DE</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>542.4</v>
+        <v>415</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -8982,22 +8982,22 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SOBA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>21.31</v>
+        <v>600.47</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -9029,30 +9029,30 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.16</v>
+        <v>1.71</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>109.82</v>
+        <v>261.26</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -9080,26 +9080,26 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5R02</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>13.35</v>
+        <v>83.66</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -9135,22 +9135,22 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>11.84</v>
+        <v>1.33</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-06-01 12:29</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>20.96</v>
+        <v>109.33</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -9182,26 +9182,26 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-06-01 12:30</t>
+          <t>2026-06-02 11:03</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AIR.MC</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>176.6</v>
+        <v>42.46</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -9233,26 +9233,26 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>0.48</v>
+        <v>1.24</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:04</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ACS.MC</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>308.17</v>
+        <v>122</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -9284,26 +9284,26 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>1.67</v>
+        <v>0.08</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-06-01 12:32</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>WF5A</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>211.14</v>
+        <v>54.84</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -9335,26 +9335,26 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>1.77</v>
+        <v>0.18</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:06</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FB2A.DE</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>380.34</v>
+        <v>520.2</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -9386,26 +9386,26 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>1.55</v>
+        <v>0.44</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>SOBA</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>70.40000000000001</v>
+        <v>21.07</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -9437,30 +9437,30 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>2.99</v>
+        <v>0.18</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MAP.MC</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3.97</v>
+        <v>109.08</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -9492,22 +9492,22 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-06-01 12:33</t>
+          <t>2026-06-02 11:07</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ENEL.MI</t>
+          <t>5R02</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>9.65</v>
+        <v>14.1</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -9539,26 +9539,26 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>0.11</v>
+        <v>11.84</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:12</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>46.42</v>
+        <v>20.83</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -9590,26 +9590,26 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>2.66</v>
+        <v>0.78</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>SAF</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>277.4</v>
+        <v>298.5</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -9641,26 +9641,26 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>1.44</v>
+        <v>0.11</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:13</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>195.88</v>
+        <v>72.86</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -9696,22 +9696,22 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>1.27</v>
+        <v>2.17</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:14</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AIR.MC</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>62.15</v>
+        <v>175.38</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -9743,26 +9743,26 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>2.24</v>
+        <v>0.25</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>NFC</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>73.90000000000001</v>
+        <v>296.41</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -9794,26 +9794,26 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>0.21</v>
+        <v>1.68</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ENR.DE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>164.18</v>
+        <v>376.37</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -9849,22 +9849,22 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-06-02 11:15</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>SAB.MC</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>154.75</v>
+        <v>2.83</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -9896,15 +9896,729 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MAP.MC</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>GRE.MC</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>121</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ENEL.MI</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>274.19</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>61.52</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
           <t>DISTRIBUYENDO</t>
         </is>
       </c>
-      <c r="J186" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>2026-06-01 12:34</t>
+      <c r="J192" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>NFC</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ENR.DE</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>152.75</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>402.69</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1542.39</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:17</t>
         </is>
       </c>
     </row>

--- a/SmartMoney_Screener.xlsx
+++ b/SmartMoney_Screener.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1174.86</v>
+        <v>546.72</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -512,26 +512,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.07</v>
+        <v>0.76</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>634.33</v>
+        <v>163.73</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -563,26 +563,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.35</v>
+        <v>0.71</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.03</v>
+        <v>450.22</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -614,26 +614,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GLBS</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.99</v>
+        <v>1216.95</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.41</v>
+        <v>0.62</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373.73</v>
+        <v>118.31</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>ISAC.L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>121.27</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.05</v>
+        <v>0.03</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>REP.MC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>495.08</v>
+        <v>23.36</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.98</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>MAP.MC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58.27</v>
+        <v>4.4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSX</t>
+          <t>CGEO.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1</v>
+        <v>4250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -920,34 +920,34 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1.13</v>
+        <v>0.02</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1064.9</v>
+        <v>184.69</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -971,38 +971,38 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>334.82</v>
+        <v>316.22</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA FUERTE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1022,30 +1022,30 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1.19</v>
+        <v>0.84</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>270.47</v>
+        <v>11.41</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1077,22 +1077,22 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1332.04</v>
+        <v>6.68</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1128,26 +1128,26 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101.65</v>
+        <v>338.31</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1179,22 +1179,22 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ZTO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.38</v>
+        <v>59.86</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1230,22 +1230,22 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.55</v>
+        <v>631.48</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1281,34 +1281,34 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>978.12</v>
+        <v>111.14</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1323,31 +1323,31 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.79</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>107.5</v>
+        <v>19.9</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1379,26 +1379,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.57</v>
+        <v>50</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>MTS.MC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1132.89</v>
+        <v>57.12</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1434,22 +1434,22 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1360.4</v>
+        <v>49.11</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1485,22 +1485,22 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>120.12</v>
+        <v>385.95</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1.07</v>
+        <v>0.65</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAB.MC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>93.66</v>
+        <v>3.2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1587,30 +1587,30 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.97</v>
+        <v>0.06</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>UNI.MC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>241.94</v>
+        <v>3.25</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1638,34 +1638,34 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.82</v>
+        <v>0.34</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23.02</v>
+        <v>73.88</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1689,26 +1689,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2.02</v>
+        <v>0.45</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CNH.AS</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.23</v>
+        <v>335.47</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1731,35 +1731,35 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>ACUMULANDO</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.87</v>
+        <v>1.64</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>491.16</v>
+        <v>291.8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1791,26 +1791,26 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>145.78</v>
+        <v>218.6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1842,22 +1842,22 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RTO</t>
+          <t>WOLF</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28.61</v>
+        <v>37.25</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1893,22 +1893,22 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.95</v>
+        <v>0.38</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>EIMI.L</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11.23</v>
+        <v>54.46</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1944,26 +1944,26 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.87</v>
+        <v>0.04</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>IBE.MC</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>268.86</v>
+        <v>20.95</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1.21</v>
+        <v>0.04</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>47.53</v>
+        <v>85.91</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2046,26 +2046,26 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>FB2A.DE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>302.7</v>
+        <v>556.4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1.21</v>
+        <v>0.08</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>NKE.DE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>213.08</v>
+        <v>37.46</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2148,26 +2148,26 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>NVD.DE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63.8</v>
+        <v>175.98</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2199,26 +2199,26 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.91</v>
+        <v>0.04</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASR</t>
+          <t>F8P</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>306.7</v>
+        <v>36.98</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2250,22 +2250,22 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.87</v>
+        <v>0.35</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CPA</t>
+          <t>TGTX</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>155.57</v>
+        <v>59.06</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2301,22 +2301,22 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VLRS</t>
+          <t>SCYR.MC</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9.369999999999999</v>
+        <v>4.81</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2343,35 +2343,35 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1.07</v>
+        <v>0.11</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BKT.MC</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7.92</v>
+        <v>15.16</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2403,26 +2403,26 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>YOOV</t>
+          <t>LOG.MC</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.77</v>
+        <v>33.88</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2454,26 +2454,26 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>21.33</v>
+        <v>0.05</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SFWL</t>
+          <t>GRF.MC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.85</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2505,26 +2505,26 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CBAT</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.59</v>
+        <v>58.49</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2556,26 +2556,26 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AERT</t>
+          <t>ENEL.MI</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.25</v>
+        <v>10.12</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2607,30 +2607,30 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0.48</v>
+        <v>0.05</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>0IE9</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>122.37</v>
+        <v>20.95</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2654,26 +2654,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1.17</v>
+        <v>0.08</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>AIR</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>509.31</v>
+        <v>136.57</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2681,11 +2681,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2705,26 +2705,26 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ACUMULANDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1.33</v>
+        <v>0.87</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CADLR</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>54.25</v>
+        <v>28.3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2732,16 +2732,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2760,39 +2760,39 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>URW</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.67</v>
+        <v>103.35</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2811,39 +2811,39 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0.88</v>
+        <v>0.03</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68.61</v>
+        <v>243.5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2862,30 +2862,30 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RYAAY</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64.75</v>
+        <v>401.11</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2913,30 +2913,30 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0.9</v>
+        <v>1.01</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>76.66</v>
+        <v>223.11</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2964,30 +2964,30 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>GLNG</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>140.49</v>
+        <v>50.87</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3015,30 +3015,30 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0.98</v>
+        <v>0.47</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>50.12</v>
+        <v>93.89</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3066,30 +3066,30 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>189.73</v>
+        <v>406.55</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3117,39 +3117,39 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>720.04</v>
+        <v>45.32</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3168,39 +3168,39 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>713.21</v>
+        <v>43.15</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3219,30 +3219,30 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>222.88</v>
+        <v>247.04</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3270,30 +3270,30 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>314.59</v>
+        <v>27.6</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3321,39 +3321,39 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>NFC</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1981.95</v>
+        <v>65.62</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3372,22 +3372,22 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0.8</v>
+        <v>0.06</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>73.34999999999999</v>
+        <v>147.12</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3395,16 +3395,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3423,30 +3423,30 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>253.16</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>COMPRA TEMPRANA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3474,30 +3474,30 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OMAB</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>113.09</v>
+        <v>384.36</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3516,39 +3516,39 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1.77</v>
+        <v>0.75</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PHOE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>17.4</v>
+        <v>358.89</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3576,22 +3576,22 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.03</v>
+        <v>0.73</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HUHU</t>
+          <t>PHM.MC</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>8.91</v>
+        <v>83.25</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>VENDIENDO</t>
+          <t>COMPRANDO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3627,22 +3627,22 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:11</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EGG</t>
+          <t>SAN.MC</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>12.1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3678,22 +3678,22 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.53</v>
+        <v>0.05</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:02</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>CABK.MC</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.13</v>
+        <v>12.57</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3725,26 +3725,26 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1.14</v>
+        <v>0.04</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:02</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>YDDL</t>
+          <t>IAG.MC</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.02</v>
+        <v>5.54</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>DEBIL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3784,30 +3784,30 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:03</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>170.08</v>
+        <v>22.33</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3831,34 +3831,34 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.88</v>
+        <v>0.06</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>18</v>
+        <v>1804.25</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3882,34 +3882,34 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>2.07</v>
+        <v>0.8</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>OVS.MI</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3.09</v>
+        <v>6.21</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>COMPRA TEMPRANA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3933,22 +3933,22 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1.08</v>
+        <v>0.05</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NCEW</t>
+          <t>3ZU0</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>17.22</v>
+        <v>64.8</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3988,30 +3988,30 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HTCO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4.21</v>
+        <v>588.66</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4026,31 +4026,31 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>COMPRANDO</t>
+          <t>VENDIENDO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.23</v>
+        <v>1.42</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:04</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FER.AS</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>59.12</v>
+        <v>41.49</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4058,11 +4058,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4086,22 +4086,22 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.06</v>
+        <v>0.59</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-01 10:08</t>
+          <t>2026-07-10 10:05</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>REL.L</t>
+          <t>IWLE.DE</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2343</v>
+        <v>10.7</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4109,50 +4109,50 @@
         </is>
       </c>
       <c r="D73" t="n">
+        <v>25</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
         <v>0</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>0.05</v>
-      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-01 10:08</t>
+          <t>2026-07-10 10:06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RTO.L</t>
+          <t>OHLA.MC</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>426.8</v>
+        <v>0.47</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4160,11 +4160,11 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4188,73 +4188,73 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-01 10:08</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>82W</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>24.97</v>
+        <v>31.2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
         <v>0</v>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>0.89</v>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CDLR</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21.91</v>
+        <v>138.26</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4290,22 +4290,22 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1.01</v>
+        <v>0.04</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:07</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ESEA</t>
+          <t>SNF</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>66.37</v>
+        <v>7.77</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4337,77 +4337,77 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>DISTRIBUYENDO</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.73</v>
+        <v>3.5</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>1B8</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6.26</v>
+        <v>6.7</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D78" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
         <v>0</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>0.32</v>
-      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GASS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7.9</v>
+        <v>158.44</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4439,26 +4439,26 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1.05</v>
+        <v>0.53</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13.43</v>
+        <v>28.24</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4494,22 +4494,22 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>1.79</v>
+        <v>0.6</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EDRY</t>
+          <t>ITX.MC</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>21.89</v>
+        <v>55.68</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4517,11 +4517,11 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4545,22 +4545,22 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.87</v>
+        <v>0.03</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:08</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>LUNR</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6.64</v>
+        <v>16.9</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4596,34 +4596,34 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1.96</v>
+        <v>0.55</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-01 10:09</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>170.86</v>
+        <v>265.65</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4647,22 +4647,22 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ENR.DE</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>216.47</v>
+        <v>153.74</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4694,26 +4694,26 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1.03</v>
+        <v>0.05</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>UFO</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>509.46</v>
+        <v>47.4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4749,22 +4749,22 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>0.78</v>
+        <v>0.25</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>354.24</v>
+        <v>174.43</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4800,22 +4800,22 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>161.91</v>
+        <v>11.43</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4823,11 +4823,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4851,22 +4851,22 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:09</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>143.15</v>
+        <v>22.58</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4874,11 +4874,11 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>0.96</v>
+        <v>0.65</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>BAM</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>313.13</v>
+        <v>46.17</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4949,26 +4949,26 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1.47</v>
+        <v>0.78</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-01 10:10</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>223.9</v>
+        <v>121.66</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5000,26 +5000,26 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DISTRIBUYENDO</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1.18</v>
+        <v>0.62</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>82.13</v>
+        <v>129.04</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5059,26 +5059,26 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8.99</v>
+        <v>93.88</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ESPERA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5106,22 +5106,22 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>11.21</v>
+        <v>133.59</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5157,22 +5157,22 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>0.46</v>
+        <v>0.97</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-01 10:11</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>16.22</v>
+        <v>108.84</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>DEBIL</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5208,73 +5208,73 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ZJK</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.96</v>
+        <v>198.53</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VENTA</t>
+          <t>ESPERA</t>
         </is>
       </c>
       <c r="D95" t="n">
+        <v>25</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
         <v>0</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>0.37</v>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-01 10:12</t>
+          <t>2026-07-10 10:10</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ANPA</t>
+          <t>ADS.DE</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4.3</v>
+        <v>181.15</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5282,39 +5282,3813 @@
         </is>
       </c>
       <c r="D96" t="n">
+        <v>25</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BSX</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>25</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ENO.MC</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>15</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ANA.MC</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>249.4</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>15</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>251</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>15</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>15</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AZM.MI</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>COMPRA TEMPRANA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>15</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>15</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CASY</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>822</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>15</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>327.87</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>15</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SPCE</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>15</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ENGI</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>15</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>15</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ELG.DE</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>15</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SATL</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>15</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>112.54</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>15</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>GNTX</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>15</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ACUMULANDO</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1SOFI.MI</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>15</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>COMPRANDO</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IFX.DE</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
         <v>0</v>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>DEBIL</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>VENDIENDO</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>NEUTRO</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>2026-07-01 10:12</t>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>YDX</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>186.84</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>938.39</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DOCN</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>140.84</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MTE.DE</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>845.6</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>991.64</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>OHB.DE</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TEVA</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MSGE</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ACS.MC</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ACX.MC</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FER.MC</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WF5A</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SPX.DE</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>131.02</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>RQ0</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SOBA</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>5R02</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>3UX</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ESPERA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BBAI</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>GRE.MC</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MVC.MC</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ANE.MC</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MEL.MC</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HOT.DE</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>465.6</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ABBN.SW</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>RIO.L</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>6764</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DAN.MI</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>NHY.OL</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>86.14</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>140.05</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>243.27</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>257.02</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>RCAT</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>327.24</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>191.11</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SEDG</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>578.05</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>436.96</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>186.99</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AMPX</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>KODK</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DHI</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>149.55</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SHEN</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>EOSE</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>44.77</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>144.22</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>IES.L</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>24</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OBDC</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>FCEL</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>23</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>DISTRIBUYENDO</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>DEBIL</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>VENDIENDO</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:11</t>
         </is>
       </c>
     </row>
